--- a/_robocze/arkusz-wzorcowy/arkusz-irin.xlsx
+++ b/_robocze/arkusz-wzorcowy/arkusz-irin.xlsx
@@ -146,7 +146,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF858A98"/>
+        <fgColor rgb="FF858B98"/>
       </patternFill>
     </fill>
     <fill>
@@ -492,7 +492,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="858A98"/>
+              <a:srgbClr val="858B98"/>
             </a:solidFill>
             <a:ln w="9000">
               <a:solidFill>
@@ -701,7 +701,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="858A98"/>
+              <a:srgbClr val="858B98"/>
             </a:solidFill>
             <a:ln w="9000">
               <a:solidFill>
@@ -911,7 +911,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="858A98"/>
+              <a:srgbClr val="858B98"/>
             </a:solidFill>
             <a:ln w="9000">
               <a:solidFill>
@@ -1132,7 +1132,7 @@
           <spPr>
             <a:ln w="18000">
               <a:solidFill>
-                <a:srgbClr val="858A98"/>
+                <a:srgbClr val="858B98"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2616,12 +2616,12 @@
       </c>
       <c r="C16" s="46" t="inlineStr">
         <is>
-          <t>#858A98</t>
+          <t>#858B98</t>
         </is>
       </c>
       <c r="D16" s="39" t="inlineStr">
         <is>
-          <t>3,11:1</t>
+          <t>3,08:1</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
